--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>97567</v>
+        <v>98092</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>97567</v>
+        <v>98092</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98092</v>
+        <v>98102</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98102</v>
+        <v>98114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98114</v>
+        <v>98119</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,11 +794,6 @@
       </c>
       <c r="E3" t="n">
         <v>219790</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -993,7 +988,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98119</v>
+        <v>98128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,11 +1002,6 @@
       </c>
       <c r="E5" t="n">
         <v>219790</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Fläcknycklar</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,6 +794,11 @@
       </c>
       <c r="E3" t="n">
         <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -988,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98128</v>
+        <v>98141</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,6 +1007,11 @@
       </c>
       <c r="E5" t="n">
         <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98141</v>
+        <v>98154</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98154</v>
+        <v>98157</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113966186</v>
       </c>
       <c r="B3" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>113966184</v>
       </c>
       <c r="B5" t="n">
-        <v>98158</v>
+        <v>98161</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 42203-2022 artfynd.xlsx
+++ b/artfynd/A 42203-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113966180</v>
+        <v>113966182</v>
       </c>
       <c r="B2" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603056</v>
+        <v>603034</v>
       </c>
       <c r="R2" t="n">
-        <v>6823082</v>
+        <v>6823077</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113966186</v>
+        <v>113966178</v>
       </c>
       <c r="B3" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +802,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603203</v>
+        <v>603054</v>
       </c>
       <c r="R3" t="n">
-        <v>6822864</v>
+        <v>6822986</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113966185</v>
+        <v>113966184</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,34 +889,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tjännavallen-Östra Bölan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603190</v>
+        <v>603098</v>
       </c>
       <c r="R4" t="n">
-        <v>6822886</v>
+        <v>6822956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,15 +984,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113966184</v>
+        <v>113966186</v>
       </c>
       <c r="B5" t="n">
-        <v>98264</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,7 +1014,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1039,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603098</v>
+        <v>603203</v>
       </c>
       <c r="R5" t="n">
-        <v>6822956</v>
+        <v>6822864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,6 +1087,200 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113966180</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjännavallen-Östra Bölan, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>603056</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6823082</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Viktor Bolin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Viktor Bolin, Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113966185</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjännavallen-Östra Bölan, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603190</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6822886</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Viktor Bolin</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Viktor Bolin, Max Ljungkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
